--- a/docs/INVERTA_UAT_Test_Cases_v2.0.xlsx
+++ b/docs/INVERTA_UAT_Test_Cases_v2.0.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -579,108 +579,112 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Learner for retakes</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>siswa2@test.local — RESERVED for E-05. Do NOT pass its session test. Passing is permanent and attempts are never deleted, so once passed the retry control is correctly hidden for ever and E-05 can never be run on that account again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>admin@academy.local</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Passwords are deliberately not written here. Ask your lead once, then keep them yourself. Kata sandi sengaja tidak ditulis di sini. Tanyakan ke lead Anda.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Passwords are deliberately not written here. Ask your lead once, then keep them yourself. Kata sandi sengaja tidak ditulis di sini. Tanyakan ke lead Anda.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>3. HOW TO GET A TOKEN (API sheet only)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Step 1</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>curl -s -X POST https://inverta.recosta.id/api/auth/login -H 'content-type: application/json' -d '{"email":"siswa@test.local","password":"&lt;ask your lead&gt;"}'</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Copy the value of "accessToken" from the reply. Paste it wherever a case shows &lt;token&gt;.</t>
+          <t>curl -s -X POST https://inverta.recosta.id/api/auth/login -H 'content-type: application/json' -d '{"email":"siswa@test.local","password":"&lt;ask your lead&gt;"}'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>The token stops working after 15 minutes. Repeat step 1 to get a new one.</t>
+          <t>Copy the value of "accessToken" from the reply. Paste it wherever a case shows &lt;token&gt;.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>The token stops working after 15 minutes. Repeat step 1 to get a new one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Admin token</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Same two steps, using admin@academy.local.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>4. HOW TO RUN A CASE</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>• Read Preconditions first. If they are not true, make them true before you start.</t>
-        </is>
-      </c>
+      <c r="B26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Baca Prasyarat dulu. Kalau belum terpenuhi, penuhi dulu sebelum mulai.</t>
+          <t>• Read Preconditions first. If they are not true, make them true before you start.</t>
         </is>
       </c>
     </row>
@@ -688,7 +692,7 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>• Follow the steps exactly, in order. Do not skip or combine steps.</t>
+          <t xml:space="preserve">  Baca Prasyarat dulu. Kalau belum terpenuhi, penuhi dulu sebelum mulai.</t>
         </is>
       </c>
     </row>
@@ -696,7 +700,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ikuti langkah persis, berurutan. Jangan melewati atau menggabungkan langkah.</t>
+          <t>• Follow the steps exactly, in order. Do not skip or combine steps.</t>
         </is>
       </c>
     </row>
@@ -704,7 +708,7 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>• Compare what you see with the Expected Result. They must match exactly.</t>
+          <t xml:space="preserve">  Ikuti langkah persis, berurutan. Jangan melewati atau menggabungkan langkah.</t>
         </is>
       </c>
     </row>
@@ -712,7 +716,7 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bandingkan yang Anda lihat dengan Hasil yang Diharapkan. Harus sama persis.</t>
+          <t>• Compare what you see with the Expected Result. They must match exactly.</t>
         </is>
       </c>
     </row>
@@ -720,7 +724,7 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>• Fill Result with Pass or Fail. If Fail, write EXACTLY what you saw in Notes.</t>
+          <t xml:space="preserve">  Bandingkan yang Anda lihat dengan Hasil yang Diharapkan. Harus sama persis.</t>
         </is>
       </c>
     </row>
@@ -728,7 +732,7 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Isi Hasil dengan Pass atau Fail. Kalau Fail, tulis persis apa yang Anda lihat.</t>
+          <t>• Fill Result with Pass or Fail. If Fail, write EXACTLY what you saw in Notes.</t>
         </is>
       </c>
     </row>
@@ -736,7 +740,7 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>• A case you cannot start is Blocked, not Fail. Say why in Notes.</t>
+          <t xml:space="preserve">  Isi Hasil dengan Pass atau Fail. Kalau Fail, tulis persis apa yang Anda lihat.</t>
         </is>
       </c>
     </row>
@@ -744,7 +748,7 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kasus yang tidak bisa dimulai adalah Blocked, bukan Fail. Tulis alasannya.</t>
+          <t>• A case you cannot start is Blocked, not Fail. Say why in Notes.</t>
         </is>
       </c>
     </row>
@@ -752,7 +756,7 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>• Text in "quotes" is exactly what appears on screen, in Indonesian.</t>
+          <t xml:space="preserve">  Kasus yang tidak bisa dimulai adalah Blocked, bukan Fail. Tulis alasannya.</t>
         </is>
       </c>
     </row>
@@ -760,7 +764,7 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Teks dalam "tanda kutip" persis seperti di layar, dalam Bahasa Indonesia.</t>
+          <t>• Text in "quotes" is exactly what appears on screen, in Indonesian.</t>
         </is>
       </c>
     </row>
@@ -768,7 +772,7 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>• Run cases in ID order unless a case says otherwise. Some cases are one-shot and say so — read those before starting them.</t>
+          <t xml:space="preserve">  Teks dalam "tanda kutip" persis seperti di layar, dalam Bahasa Indonesia.</t>
         </is>
       </c>
     </row>
@@ -776,171 +780,179 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Jalankan sesuai urutan ID kecuali kasus menyebutkan lain. Beberapa kasus hanya bisa sekali dan menyebutkannya — baca dulu sebelum menjalankannya.</t>
+          <t>• Run cases in ID order unless a case says otherwise. Some cases are one-shot and say so — read those before starting them.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Jalankan sesuai urutan ID kecuali kasus menyebutkan lain. Beberapa kasus hanya bisa sekali dan menyebutkannya — baca dulu sebelum menjalankannya.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>5. NOT PART OF THIS BUILD — DO NOT RAISE BUGS</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
+          <t>5. NOT PART OF THIS BUILD — DO NOT RAISE BUGS</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
           <t>Bukan bagian dari build ini — jangan laporkan sebagai bug</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>✗ Real emails</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Emails are written to the server log, not sent. You will never receive one. Email verification therefore cannot be completed by a real inbox.</t>
-        </is>
-      </c>
+      <c r="B43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>✗ Google sign-in</t>
+          <t>✗ Real emails</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>The "Lanjutkan dengan Google" button is visible but was never connected. It will not work.</t>
+          <t>Emails are written to the server log, not sent. You will never receive one. Email verification therefore cannot be completed by a real inbox.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>✗ Real payment</t>
+          <t>✗ Google sign-in</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Payment uses a built-in simulator with a succeed and a fail button. No real money, no real gateway.</t>
+          <t>The "Lanjutkan dengan Google" button is visible but was never connected. It will not work.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>✗ Video content</t>
+          <t>✗ Real payment</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Every session plays the same sample clip on purpose.</t>
+          <t>Payment uses a built-in simulator with a succeed and a fail button. No real money, no real gateway.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>✗ Exam question wording</t>
+          <t>✗ Video content</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>The final exam holds 140 PLACEHOLDER questions. Every one starts with "[CONTOH]". They exist so the exam can be tested; they are not real TOEFL content. Do not report their wording, difficulty or answers as bugs.</t>
+          <t>Every session plays the same sample clip on purpose.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>✗ Listening audio quality</t>
+          <t>✗ Exam question wording</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>The sample audio is computer-generated on purpose. A robotic voice is expected.</t>
+          <t>The final exam holds 140 PLACEHOLDER questions. Every one starts with "[CONTOH]". They exist so the exam can be tested; they are not real TOEFL content. Do not report their wording, difficulty or answers as bugs.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>✗ Listening audio quality</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>The sample audio is computer-generated on purpose. A robotic voice is expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>✗ Section time-out message</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>When a section's time runs out the exam moves on silently. There is no "waktu habis" message in this build. Do not report the absence as a bug.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr"/>
-    </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>6. WHAT IS IN THIS PACK</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>API test cases</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>25</v>
-      </c>
+      <c r="B52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>UI test cases</t>
+          <t>API test cases</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>UI test cases</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B55" s="2" t="n">
         <v>81</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Cases marked SECURITY must be reported to the lead IMMEDIATELY if they fail — do not wait until the end of the run.</t>
-        </is>
-      </c>
+      <c r="B56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Cases marked SECURITY must be reported to the lead IMMEDIATELY if they fail — do not wait until the end of the run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Kasus bertanda SECURITY harus dilaporkan ke lead SEGERA jika gagal — jangan menunggu sampai pengujian selesai.</t>
         </is>
@@ -2669,94 +2681,216 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>E-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Session test / Tes sesi</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>A failed session test can be retaken.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Tes sesi yang gagal dapat diulang.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sign in as siswa2@test.local — the account RESERVED for this case. It is enrolled and has never taken the test. Do NOT use siswa@test.local: it has already passed, and passing is permanent, so the retry control is correctly hidden there.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Masuk sebagai siswa2@test.local — akun KHUSUS untuk kasus ini. Sudah terdaftar dan belum pernah mengerjakan tes. JANGAN pakai siswa@test.local: akun itu sudah lulus, dan kelulusan bersifat permanen, sehingga tombol ulang memang tidak ditampilkan di sana.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Open session 1 and watch the video past ~90% so the test unlocks.
+2. Answer all 15 questions DELIBERATELY WRONG — pick the first choice every time.
+3. Click "Kirim jawaban".
+4. Without leaving the page, look at the bottom right of the test panel.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1. Buka sesi 1 dan tonton video sampai lewat ~90% agar tes terbuka.
+2. Jawab ke-15 soal SENGAJA SALAH — pilih opsi pertama setiap kali.
+3. Klik "Kirim jawaban".
+4. Tanpa meninggalkan halaman, lihat kanan bawah panel tes.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>A button reads "Coba lagi" and is clickable. It does NOT read "Batas percobaan tercapai" — this test has no attempt limit. Clicking it clears the answers and reopens the 15 questions.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Muncul tombol "Coba lagi" yang dapat diklik. TIDAK bertuliskan "Batas percobaan tercapai" — tes ini tanpa batas percobaan. Mengkliknya mengosongkan jawaban dan membuka kembali ke-15 soal.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="92" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Listening audio / Audio listening</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Listening questions in a session test can be played.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Soal Listening pada tes sesi dapat diputar.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The session 1 test is open (watch the video past ~90% first). Questions 1-5 are Listening and each has its own recording.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tes sesi 1 terbuka (tonton video lewat ~90% dulu). Soal 1-5 adalah Listening dan masing-masing punya rekaman sendiri.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the session 1 test and look at question 1.
+2. Click "▶ Putar audio".
+3. Wait for the player to appear and listen for about 10 seconds.
+4. Check questions 2 to 5 also have the button, and question 6 onward does not.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>1. Buka tes sesi 1 dan lihat soal 1.
+2. Klik "▶ Putar audio".
+3. Tunggu pemutar muncul lalu dengarkan sekitar 10 detik.
+4. Periksa soal 2 sampai 5 juga punya tombolnya, dan soal 6 ke atas tidak.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>An audio player appears and plays a voice reading a short conversation, matching the question on screen. Only Listening questions show the button. (A robotic voice is expected — see the Info sheet.) You may replay as often as you like: a session test has no play limit, unlike the final exam.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Muncul pemutar audio yang memutar suara membacakan percakapan singkat, sesuai soal di layar. Hanya soal Listening yang punya tombolnya. (Suara robot itu wajar — lihat sheet Info.) Anda boleh memutar ulang sesering mungkin: tes sesi tanpa batas pemutaran, berbeda dengan tes akhir.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>UI-EXAM-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>The final assessment is locked until every earlier session is complete.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tes akhir terkunci sampai semua sesi sebelumnya selesai.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local with ACTIVE access, and at least one earlier session not yet complete.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local dengan akses AKTIF, dan minimal satu sesi sebelumnya belum selesai.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Open https://inverta.recosta.id/app/dashboard and open the programme.
 2. Find the last session in the list, named "Tes Akhir: Simulasi TOEFL ITP".
 3. Try to open it.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/app/dashboard lalu buka programnya.
 2. Cari sesi terakhir bernama "Tes Akhir: Simulasi TOEFL ITP".
 3. Coba buka sesi itu.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>The session is shown as locked and does not open. No exam starts.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Sesi ditampilkan terkunci dan tidak terbuka. Tidak ada tes yang dimulai.</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="92" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-02</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>The exam starts on Listening, with a countdown and an audio button.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tes dimulai pada Listening, dengan hitung mundur dan tombol audio.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Every earlier session complete. TAKES 5 MINUTES TO SET UP. This case STARTS the learner's only attempt — see UI-EXAM-06 before you run it.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Semua sesi sebelumnya selesai. BUTUH 5 MENIT PERSIAPAN. Kasus ini MEMULAI satu-satunya percobaan pelajar — baca UI-EXAM-06 sebelum menjalankannya.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Open the final session.
 2. Read the notice on the intro screen.
@@ -2764,7 +2898,7 @@
 4. Look at the top of the exam screen.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1. Buka sesi terakhir.
 2. Baca pemberitahuan di layar pembuka.
@@ -2772,520 +2906,520 @@
 4. Lihat bagian atas layar tes.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>The intro screen states the score is an INVERTA prediction and not an official ETS TOEFL result. After starting, the screen shows Listening questions, a countdown that is ticking down, and a button to play the audio.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Layar pembuka menyatakan skor adalah prediksi INVERTA dan bukan skor TOEFL resmi dari ETS. Setelah dimulai, layar menampilkan soal Listening, hitung mundur yang berjalan, dan tombol untuk memutar audio.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="92" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-03</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>The audio can only be played the allowed number of times.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Audio hanya dapat diputar sebanyak jatah yang diizinkan.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Run UI-EXAM-02 first and stay on the Listening section.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-EXAM-02 dulu dan tetap di bagian Listening.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Read the play button — it shows how many plays are left.
 2. Click it once and let the clip finish.
 3. Read the button again and click it.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1. Baca tombol putar — tertulis sisa jatah pemutaran.
 2. Klik sekali dan biarkan klip selesai.
 3. Baca lagi tombolnya dan klik.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>After the allowance is used the button shows no plays left and clicking it does not start the audio again.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Setelah jatah habis, tombol menunjukkan sisa nol dan mengkliknya tidak memutar audio lagi.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-04</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Moving to the next section is one-way and the screen says so before you do it.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Pindah ke bagian berikutnya bersifat satu arah dan layar memberitahukannya lebih dulu.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Run UI-EXAM-02 first. IRREVERSIBLE: you cannot return to Listening afterwards.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-EXAM-02 dulu. TIDAK DAPAT DIBATALKAN: Anda tidak bisa kembali ke Listening.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1. Read the note under the next-section button.
 2. Click the next-section button.
 3. Look for any way back to Listening — a button, a link, a tab, the browser Back button.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1. Baca catatan di bawah tombol bagian berikutnya.
 2. Klik tombol bagian berikutnya.
 3. Cari cara kembali ke Listening — tombol, tautan, tab, atau tombol Back peramban.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>The note warns you cannot come back. After clicking, Structure questions are shown and there is no way at all to return to Listening.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Catatan memperingatkan Anda tidak bisa kembali. Setelah diklik, soal Structure ditampilkan dan tidak ada cara apa pun kembali ke Listening.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="92" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Finishing the exam shows a predicted score and issues a certificate.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Menyelesaikan tes menampilkan skor prediksi dan menerbitkan sertifikat.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Run UI-EXAM-04 twice so you are on Reading. IRREVERSIBLE: this uses up the account's only attempt. Run UI-EXAM-06 after this, never before.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-EXAM-04 dua kali sampai Anda di Reading. TIDAK DAPAT DIBATALKAN: ini menghabiskan satu-satunya percobaan akun. Jalankan UI-EXAM-06 setelah ini, jangan sebelumnya.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. Answer some Reading questions.
 2. Click the finish button.
 3. Read the result screen from top to bottom.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1. Jawab beberapa soal Reading.
 2. Klik tombol selesai.
 3. Baca layar hasil dari atas sampai bawah.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>A predicted TOEFL score between 310 and 677 is shown. The screen states plainly that this is an INVERTA prediction and NOT an official ETS TOEFL result. A link to the certificate is offered.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Skor prediksi TOEFL antara 310 dan 677 ditampilkan. Layar menyatakan dengan jelas ini prediksi INVERTA dan BUKAN skor TOEFL resmi dari ETS. Tersedia tautan ke sertifikat.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="92" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-06</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>A second attempt is refused once the single attempt is used.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Percobaan kedua ditolak setelah satu-satunya percobaan terpakai.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Run UI-EXAM-05 first. Run this AFTER it, never before.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-EXAM-05 dulu. Jalankan ini SESUDAHNYA, jangan sebelumnya.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Open the final session again.
 2. Look at the button on the intro screen.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>1. Buka lagi sesi terakhir.
 2. Lihat tombol di layar pembuka.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>The button says the attempt limit is reached and cannot be clicked. The exam does not restart.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Tombol menyatakan batas percobaan tercapai dan tidak bisa diklik. Tes tidak dimulai ulang.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="92" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>The certificate can be verified by anyone, without signing in.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sertifikat dapat diverifikasi siapa pun, tanpa masuk.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Run UI-EXAM-05 first and open the certificate to copy its verification code.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-EXAM-05 dulu dan buka sertifikat untuk menyalin kode verifikasinya.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. Open a private/incognito window so you are signed out.
 2. Go to https://inverta.recosta.id/verify/&lt;the code you copied&gt;.
 3. Read the page.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1. Buka jendela penyamaran agar Anda dalam keadaan keluar.
 2. Buka https://inverta.recosta.id/verify/&lt;kode yang Anda salin&gt;.
 3. Baca halamannya.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>The page loads without signing in, shows the learner name and the predicted score, and states it is an INVERTA prediction, not an official ETS TOEFL result.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Halaman terbuka tanpa masuk, menampilkan nama pelajar dan skor prediksi, serta menyatakan ini prediksi INVERTA, bukan skor TOEFL resmi dari ETS.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="92" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="92" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>UI-EXAM-08</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Final assessment / Tes akhir</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>An unknown certificate code shows a not-found message, not an error page.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Kode sertifikat tidak dikenal menampilkan pesan tidak ditemukan, bukan halaman error.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>None. You can be signed out.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tidak ada. Anda boleh dalam keadaan keluar.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/verify/NOTAREALCODE123.
 2. Read the page.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/verify/NOTAREALCODE123.
 2. Baca halamannya.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>The page loads normally and says the certificate was not found. It does NOT show a certificate, and it is not a browser error page.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Halaman terbuka normal dan menyatakan sertifikat tidak ditemukan. TIDAK menampilkan sertifikat, dan bukan halaman error peramban.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10" ht="92" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="92" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>UI-ADM-08</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Admin — Learners / Peserta</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>A revoked learner can be restored from the enrollment row.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Pelajar yang dicabut dapat dipulihkan dari baris pendaftarannya.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Signed in as admin, and siswa@test.local has been revoked (run I-02 first).</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai admin, dan siswa@test.local sudah dicabut (jalankan I-02 dulu).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/admin/enrollments and find siswa@test.local. Its status is "Dicabut".
 2. Click "Pulihkan" on that row and confirm.
 3. Read the status column.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/admin/enrollments lalu cari siswa@test.local. Statusnya "Dicabut".
 2. Klik "Pulihkan" pada baris itu lalu konfirmasi.
 3. Baca kolom status.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>The status returns to "Aktif". Only ONE row exists for that learner — restoring must not create a second enrollment. Their earlier progress is still there.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Status kembali menjadi "Aktif". Hanya ADA SATU baris untuk pelajar itu — memulihkan tidak boleh membuat pendaftaran kedua. Progres sebelumnya masih ada.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="92" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="92" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>UI-IMP-01</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Admin — Bulk import / Impor massal</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>The question import template can be downloaded and it opens in Excel.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Template impor soal dapat diunduh dan terbuka di Excel.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Signed in as admin.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai admin.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/admin/questions/import.
 2. Click the template download button.
 3. Open the downloaded file.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/admin/questions/import.
 2. Klik tombol unduh template.
 3. Buka berkas yang terunduh.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>An .xlsx file downloads and opens without a repair prompt. It has sheets named "Questions", "Passages" and "Instructions", and the Questions sheet already has example rows.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Berkas .xlsx terunduh dan terbuka tanpa permintaan perbaikan. Ada sheet bernama "Questions", "Passages" dan "Instructions", dan sheet Questions sudah berisi contoh baris.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12" ht="92" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="92" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>UI-IMP-02</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Admin — Bulk import / Impor massal</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>A sheet with a mistake is refused and every mistake is listed with its row and column.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Berkas dengan kesalahan ditolak dan setiap kesalahan didaftar beserta baris dan kolomnya.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Run UI-IMP-01 first. In the template, change the "section" cell of the first example row to "Speaking" and save.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Jalankan UI-IMP-01 dulu. Pada template, ubah sel "section" baris contoh pertama menjadi "Speaking" lalu simpan.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/admin/questions/import.
 2. Choose your edited file.
@@ -3293,7 +3427,7 @@
 4. Read the error table.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/admin/questions/import.
 2. Pilih berkas yang Anda ubah.
@@ -3301,168 +3435,168 @@
 4. Baca tabel kesalahan.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>An error table appears naming the ROW NUMBER and the COLUMN "section", and says which section names are allowed. The import button stays disabled — nothing is saved.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Muncul tabel kesalahan yang menyebutkan NOMOR BARIS dan KOLOM "section", serta menyatakan nama bagian yang diizinkan. Tombol impor tetap nonaktif — tidak ada yang tersimpan.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="92" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="92" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>A-01</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Access / Akses</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>The public program page opens and shows the price.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Halaman program publik terbuka dan menampilkan harga.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>None. You are signed out.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tidak ada. Anda dalam keadaan keluar (logout).</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Open a browser and go to https://inverta.recosta.id
 2. Look at the page that loads.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1. Buka browser dan kunjungi https://inverta.recosta.id
 2. Perhatikan halaman yang muncul.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>The page shows the title "INVERTA — Persiapan TOEFL", the price "Rp 1.500.000", the words "/ sekali bayar", and a button "Masuk &amp; daftar".</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Halaman menampilkan judul "INVERTA — Persiapan TOEFL", harga "Rp 1.500.000", tulisan "/ sekali bayar", dan tombol "Masuk &amp; daftar".</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="92" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="92" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>A-02</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Access / Akses</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>A new account can be registered.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Akun baru dapat didaftarkan.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>You are signed out. Invent an email nobody has used, e.g. qa1@test.local</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Anda logout. Buat email yang belum pernah dipakai, misal qa1@test.local</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/register
 2. Fill Name, Email (your invented one), and Password (at least 8 characters, e.g. Qa123456!)
 3. Submit the form.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/register
 2. Isi Nama, Email (yang Anda buat), dan Kata sandi (minimal 8 karakter, misal Qa123456!)
 3. Kirim formulir.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>You are signed in and taken into the app. No error is shown.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Anda otomatis masuk dan diarahkan ke dalam aplikasi. Tidak ada pesan error.</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="92" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="92" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>A-04</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Access / Akses</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>The learner account can sign in and sign out.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Akun siswa dapat masuk dan keluar.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>You are signed out.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Anda dalam keadaan logout.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/login
 2. Sign in as siswa@test.local / Siswa12345!
@@ -3471,7 +3605,7 @@
 5. Try to open https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/login
 2. Masuk sebagai siswa@test.local / Siswa12345!
@@ -3480,168 +3614,168 @@
 5. Coba buka https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Step 3 opens a small menu showing your name and email. Step 4 signs you out. Step 5 sends you back to the sign-in page instead of the dashboard.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Langkah 3 membuka menu kecil berisi nama dan email Anda. Langkah 4 mengeluarkan Anda. Langkah 5 mengarahkan kembali ke halaman login, bukan dashboard.</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="92" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="92" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Enrollment / Pendaftaran</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>An enrolled learner sees the program on their dashboard.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Siswa terdaftar melihat programnya di dashboard.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local (already enrolled).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local (sudah terdaftar).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as siswa@test.local / Siswa12345!
 2. Go to https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1. Masuk sebagai siswa@test.local / Siswa12345!
 2. Buka https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>The dashboard lists "INVERTA — Persiapan TOEFL" with status Active, and a button "Lanjutkan". It does NOT say "Belum ada program aktif".</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Dashboard menampilkan "INVERTA — Persiapan TOEFL" berstatus Active dan tombol "Lanjutkan". TIDAK muncul "Belum ada program aktif".</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="92" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="92" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>B-02</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Enrollment / Pendaftaran</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>A brand-new, unpaid account has no access to the programme.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Akun baru yang belum membayar tidak punya akses ke program.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The account you created in A-02, signed in, which has never paid.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Akun yang Anda buat di A-02, sudah masuk, dan belum pernah membayar.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Sign in with your A-02 account.
 2. Go to https://inverta.recosta.id/app/dashboard
 3. Read what is shown.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1. Masuk dengan akun A-02 Anda.
 2. Buka https://inverta.recosta.id/app/dashboard
 3. Baca yang ditampilkan.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>The dashboard shows "Belum ada program aktif". No lesson or session is reachable.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Dashboard menampilkan "Belum ada program aktif". Tidak ada sesi atau pelajaran yang bisa dibuka.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18" ht="92" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="92" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Enrollment / Pendaftaran</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Starting checkout alone does NOT grant access. This is a critical rule.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Memulai checkout saja TIDAK memberi akses. Ini aturan penting.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Your A-02 account, signed in, never paid.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Akun A-02 Anda, sudah masuk, belum pernah membayar.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. Sign in with your A-02 account.
 2. Go to https://inverta.recosta.id/program/toefl-preparation
@@ -3649,7 +3783,7 @@
 4. When the payment page opens, DO NOT pay. Go back to https://inverta.recosta.id/app/dashboard instead.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1. Masuk dengan akun A-02 Anda.
 2. Buka https://inverta.recosta.id/program/toefl-preparation
@@ -3657,246 +3791,132 @@
 4. Saat halaman pembayaran terbuka, JANGAN bayar. Kembali ke https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Access is still NOT granted. The dashboard still shows no active programme, or shows the programme as PendingPayment. No session can be opened.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Akses tetap TIDAK diberikan. Dashboard tetap tanpa program aktif, atau program berstatus PendingPayment. Tidak ada sesi yang bisa dibuka.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="92" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="92" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Enrollment / Pendaftaran</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Completing the simulated payment grants access.</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Menyelesaikan pembayaran simulasi memberikan akses.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Continue directly from B-03, same account.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Lanjutkan langsung dari B-03, akun yang sama.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Go to https://inverta.recosta.id/program/toefl-preparation and click "Daftar sekarang".
 2. On the simulated payment page, choose the option that completes/succeeds the payment.
 3. Go to https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>1. Buka https://inverta.recosta.id/program/toefl-preparation lalu klik "Daftar sekarang".
 2. Di halaman pembayaran simulasi, pilih opsi yang menyelesaikan/menyukseskan pembayaran.
 3. Buka https://inverta.recosta.id/app/dashboard</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>The programme now appears with status Active and a "Lanjutkan" button. Session 1 can be opened.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Program kini muncul berstatus Active dengan tombol "Lanjutkan". Sesi 1 bisa dibuka.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20" ht="92" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="92" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Linear lock / Kunci berurutan</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Only the first session is open; every later session is locked.</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Hanya sesi pertama yang terbuka; sesi berikutnya terkunci.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local, who has not completed any session yet.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local yang belum menyelesaikan sesi apa pun.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as siswa@test.local / Siswa12345!
 2. Open the programme from the dashboard.
 3. Look at the list of 8 sessions and note which are open and which are locked.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1. Masuk sebagai siswa@test.local / Siswa12345!
 2. Buka program dari dashboard.
 3. Lihat daftar 8 sesi dan catat mana yang terbuka dan mana yang terkunci.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>"Sesi 1: Mengenal Format &amp; Strategi TOEFL" is open. Sessions 2 to 8 are all marked locked ("Locked" / "Sesi terkunci").</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>"Sesi 1: Mengenal Format &amp; Strategi TOEFL" terbuka. Sesi 2 sampai 8 semuanya terkunci ("Locked" / "Sesi terkunci").</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="92" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>C-02</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Linear lock / Kunci berurutan</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>A locked session cannot be opened even by typing its address directly.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Sesi terkunci tidak bisa dibuka walau alamatnya diketik langsung.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Continue from C-01. Session 1 is NOT yet completed.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Lanjutkan dari C-01. Sesi 1 BELUM diselesaikan.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. On the programme page, click "Sesi 2: Listening — Short Conversations".
-2. If clicking does nothing, copy the address of session 2 and paste it into the browser address bar, then press Enter.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1. Di halaman program, klik "Sesi 2: Listening — Short Conversations".
-2. Jika klik tidak berfungsi, salin alamat sesi 2 lalu tempel di kolom alamat browser dan tekan Enter.</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Session 2 does not open. You see a locked message and no video player. You must NOT be able to reach the lesson.</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Sesi 2 tidak terbuka. Muncul pesan terkunci dan tidak ada pemutar video. Anda TIDAK boleh bisa masuk ke pelajaran.</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22" ht="92" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>C-03</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Linear lock / Kunci berurutan</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Finishing session 1 unlocks session 2 only, not the whole programme.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Menyelesaikan sesi 1 hanya membuka sesi 2, bukan seluruh program.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Session 1 has just been completed (do E-04 first).</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Sesi 1 baru saja diselesaikan (kerjakan E-04 dulu).</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1. After passing the session 1 test, return to the programme page.
-2. Check the state of sessions 2 and 3.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1. Setelah lulus tes sesi 1, kembali ke halaman program.
-2. Periksa status sesi 2 dan sesi 3.</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Session 1 is Completed. Session 2 is now open. Session 3 is STILL locked. Only one session unlocks at a time.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Sesi 1 berstatus Completed. Sesi 2 kini terbuka. Sesi 3 MASIH terkunci. Hanya satu sesi terbuka setiap kali.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
@@ -3906,94 +3926,208 @@
     <row r="23" ht="92" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Linear lock / Kunci berurutan</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>A locked session cannot be opened even by typing its address directly.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sesi terkunci tidak bisa dibuka walau alamatnya diketik langsung.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Continue from C-01. Session 1 is NOT yet completed.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Lanjutkan dari C-01. Sesi 1 BELUM diselesaikan.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. On the programme page, click "Sesi 2: Listening — Short Conversations".
+2. If clicking does nothing, copy the address of session 2 and paste it into the browser address bar, then press Enter.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1. Di halaman program, klik "Sesi 2: Listening — Short Conversations".
+2. Jika klik tidak berfungsi, salin alamat sesi 2 lalu tempel di kolom alamat browser dan tekan Enter.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Session 2 does not open. You see a locked message and no video player. You must NOT be able to reach the lesson.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Sesi 2 tidak terbuka. Muncul pesan terkunci dan tidak ada pemutar video. Anda TIDAK boleh bisa masuk ke pelajaran.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Linear lock / Kunci berurutan</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Finishing session 1 unlocks session 2 only, not the whole programme.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Menyelesaikan sesi 1 hanya membuka sesi 2, bukan seluruh program.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Session 1 has just been completed (do E-04 first).</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Sesi 1 baru saja diselesaikan (kerjakan E-04 dulu).</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. After passing the session 1 test, return to the programme page.
+2. Check the state of sessions 2 and 3.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1. Setelah lulus tes sesi 1, kembali ke halaman program.
+2. Periksa status sesi 2 dan sesi 3.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Session 1 is Completed. Session 2 is now open. Session 3 is STILL locked. Only one session unlocks at a time.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Sesi 1 berstatus Completed. Sesi 2 kini terbuka. Sesi 3 MASIH terkunci. Hanya satu sesi terbuka setiap kali.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="92" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>D-01</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>The lesson video plays.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Video pelajaran dapat diputar.</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local. Session 1 is open.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local. Sesi 1 terbuka.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Open session 1.
 2. Press play on the video.
 3. Let it play for about 20 seconds.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1. Buka sesi 1.
 2. Tekan putar pada video.
 3. Biarkan berjalan sekitar 20 detik.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>The video plays with picture and sound. No error such as "Video tidak dapat diputar" appears. (The clip is a sample — see the Info sheet.)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Video berjalan dengan gambar dan suara. Tidak muncul error seperti "Video tidak dapat diputar". (Klip ini contoh — lihat sheet Info.)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="92" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="92" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>D-02</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Watch progress is remembered after leaving and coming back.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Progres menonton diingat setelah keluar dan kembali.</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local. Session 1 is open.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local. Sesi 1 terbuka.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Open session 1 and play the video for about 60 seconds.
 2. Note the progress shown on screen.
@@ -4001,7 +4135,7 @@
 4. Open session 1 again.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1. Buka sesi 1 dan putar video sekitar 60 detik.
 2. Catat progres yang tampil di layar.
@@ -4009,170 +4143,170 @@
 4. Buka sesi 1 lagi.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>The progress from step 2 is still shown. It has not reset to zero.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Progres dari langkah 2 masih tersimpan. Tidak kembali ke nol.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="92" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="92" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>D-03</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Watching the whole video does NOT complete a session that has a test.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Menonton video sampai habis TIDAK menyelesaikan sesi yang punya tes.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Session 1 has a test attached and has not been passed yet.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Sesi 1 punya tes dan belum pernah dilulusi.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Open session 1.
 2. Watch (or skip forward through) the video until progress reaches 100%.
 3. Return to the programme page and look at session 2.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>1. Buka sesi 1.
 2. Tonton (atau lewati maju) video sampai progres mencapai 100%.
 3. Kembali ke halaman program dan lihat sesi 2.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Session 1 is NOT completed and session 2 is STILL locked. Watching alone is not enough — the test must be passed too.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Sesi 1 BELUM selesai dan sesi 2 MASIH terkunci. Menonton saja tidak cukup — tes harus dilulusi juga.</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26" ht="92" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="92" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>E-01</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Session test / Tes sesi</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>The session test opens and shows 15 questions.</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tes sesi terbuka dan menampilkan 15 soal.</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Signed in as siswa@test.local. Session 1 is open.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Masuk sebagai siswa@test.local. Sesi 1 terbuka.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Open session 1.
 2. Find and open the session test ("Tes sesi").
 3. Count the questions and note their sections.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>1. Buka sesi 1.
 2. Cari dan buka tes sesi ("Tes sesi").
 3. Hitung jumlah soal dan catat bagiannya.</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>The test shows 15 questions: 5 Listening, 5 Structure, 5 Reading. Each question has 4 answer choices.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Tes menampilkan 15 soal: 5 Listening, 5 Structure, 5 Reading. Setiap soal punya 4 pilihan jawaban.</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="92" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="92" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>E-03</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Session test / Tes sesi</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Failing the test leaves the next session locked.</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tes yang tidak lulus membuat sesi berikutnya tetap terkunci.</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Session 1 test is open and has not been passed. Pass mark is 9 of 15.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Tes sesi 1 terbuka dan belum lulus. Nilai lulus 9 dari 15.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Open the session 1 test.
 2. Deliberately answer WRONGLY — pick the first choice for every one of the 15 questions.
@@ -4180,7 +4314,7 @@
 4. Read the score, then return to the programme page.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1. Buka tes sesi 1.
 2. Sengaja jawab SALAH — pilih opsi pertama untuk ke-15 soal.
@@ -4188,52 +4322,52 @@
 4. Baca skor, lalu kembali ke halaman program.</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>The result shows a score below 9 and says you did not pass. Session 2 is STILL locked.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Hasil menampilkan skor di bawah 9 dan dinyatakan tidak lulus. Sesi 2 MASIH terkunci.</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="92" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="92" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>E-04</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Session test / Tes sesi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Passing the test completes the session and unlocks the next one.</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Lulus tes menyelesaikan sesi dan membuka sesi berikutnya.</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Session 1 video has been watched to the required amount (do D-02 first). Answer key is on the 'Answer key' sheet.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Video sesi 1 sudah ditonton sesuai syarat (kerjakan D-02 dulu). Kunci jawaban ada di sheet 'Answer key'.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Open the session 1 test.
 2. Answer all 15 questions using the 'Answer key' sheet of this workbook.
@@ -4241,7 +4375,7 @@
 4. Return to the programme page.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>1. Buka tes sesi 1.
 2. Jawab ke-15 soal memakai sheet 'Answer key' di workbook ini.
@@ -4249,132 +4383,14 @@
 4. Kembali ke halaman program.</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>The result shows 15 of 15 and says you passed. Session 1 becomes Completed and session 2 becomes open.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Hasil menampilkan 15 dari 15 dan dinyatakan lulus. Sesi 1 menjadi Completed dan sesi 2 terbuka.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="92" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>E-05</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Session test / Tes sesi</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>A failed test can be retaken.</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Tes yang gagal dapat diulang.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Run this IMMEDIATELY after E-03, BEFORE you run E-04. Stay on the same screen — do not reload the page or navigate away. Once the test has been passed (E-04) it is complete and this case can no longer be run; to redo it you need a learner who has not passed yet.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Kerjakan SEGERA setelah E-03, SEBELUM mengerjakan E-04. Tetap di layar yang sama — jangan muat ulang halaman atau berpindah halaman. Jika tes sudah pernah lulus (E-04), tes itu selesai dan kasus ini tidak bisa dijalankan lagi; perlu siswa lain yang belum lulus.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1. On the failed result from E-03, without leaving the page, find the "Coba lagi" button at the bottom right of the test panel.
-2. Click it. The 15 questions should reappear, unanswered.
-3. Check the button did NOT read "Batas percobaan tercapai".</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1. Pada hasil tidak lulus dari E-03, tanpa meninggalkan halaman, cari tombol "Coba lagi" di kanan bawah panel tes.
-2. Klik tombol itu. Ke-15 soal harus muncul kembali dalam keadaan kosong.
-3. Pastikan tombol TIDAK bertuliskan "Batas percobaan tercapai".</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>The test can be taken again. It does NOT say "Batas percobaan tercapai", because this test has no attempt limit.</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Tes bisa dikerjakan lagi. TIDAK muncul "Batas percobaan tercapai", karena tes ini tanpa batas percobaan.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30" ht="92" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>F-01</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Listening audio / Audio listening</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Audio plays on a Listening question.</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Audio dapat diputar pada soal Listening.</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>The session 1 test is open. Questions 1–5 are Listening.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Tes sesi 1 terbuka. Soal 1–5 adalah Listening.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the session 1 test and go to question 1.
-2. Find the audio control and press play.
-3. Listen for about 10 seconds.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1. Buka tes sesi 1 dan ke soal 1.
-2. Cari kontrol audio lalu tekan putar.
-3. Dengarkan sekitar 10 detik.</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>A voice reads a short conversation and then the question. The audio matches the question on screen. (Robotic voice is expected — see Info sheet.)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Terdengar suara membacakan percakapan singkat lalu pertanyaannya. Audio sesuai dengan soal di layar. (Suara robot itu wajar — lihat sheet Info.)</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
